--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -607,7 +607,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,7 +514,7 @@
     <t>MOPEDConditionIdentifier</t>
   </si>
   <si>
-    <t>MOPED Identifier = Aufnahmezahl+ICD10Code+Procedure.occurrence(YYYY-MM-DDTHH:MM)</t>
+    <t>MOPED Identifier = Aufnahmezahl-Procedure.code-Procedure.occurrence(YYYY-MM-DDTHH:MM)</t>
   </si>
   <si>
     <t>Procedure.identifier:MOPEDConditionIdentifier.id</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$70</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1874,6 +1877,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2213,7 +2231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2325,7 +2343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>86</v>
       </c>
@@ -2439,7 +2457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2551,7 +2569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -2665,7 +2683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -2779,7 +2797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2893,7 +2911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -3007,7 +3025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -3121,7 +3139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3237,7 +3255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3351,7 +3369,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3469,7 +3487,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3581,7 +3599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3695,7 +3713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
@@ -3811,7 +3829,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>184</v>
       </c>
@@ -3925,7 +3943,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>194</v>
       </c>
@@ -4037,7 +4055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -4151,7 +4169,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>198</v>
       </c>
@@ -4267,7 +4285,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>208</v>
       </c>
@@ -4379,7 +4397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>210</v>
       </c>
@@ -4493,7 +4511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>212</v>
       </c>
@@ -4609,7 +4627,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -4723,7 +4741,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>230</v>
       </c>
@@ -4837,7 +4855,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>240</v>
       </c>
@@ -4951,7 +4969,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>248</v>
       </c>
@@ -5067,7 +5085,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>258</v>
       </c>
@@ -5183,7 +5201,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>267</v>
       </c>
@@ -5299,7 +5317,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>277</v>
       </c>
@@ -5413,7 +5431,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>287</v>
       </c>
@@ -5525,7 +5543,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>295</v>
       </c>
@@ -5639,7 +5657,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>304</v>
       </c>
@@ -5751,7 +5769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>310</v>
       </c>
@@ -5865,7 +5883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>315</v>
       </c>
@@ -5977,7 +5995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>322</v>
       </c>
@@ -6091,7 +6109,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>331</v>
       </c>
@@ -6205,7 +6223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>340</v>
       </c>
@@ -6319,7 +6337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>350</v>
       </c>
@@ -6431,7 +6449,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>358</v>
       </c>
@@ -6450,7 +6468,7 @@
         <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -6543,7 +6561,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>368</v>
       </c>
@@ -6655,7 +6673,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>377</v>
       </c>
@@ -6767,7 +6785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>381</v>
       </c>
@@ -6881,7 +6899,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>390</v>
       </c>
@@ -6995,7 +7013,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>399</v>
       </c>
@@ -7107,7 +7125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>406</v>
       </c>
@@ -7219,7 +7237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>412</v>
       </c>
@@ -7333,7 +7351,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>421</v>
       </c>
@@ -7445,7 +7463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>428</v>
       </c>
@@ -7557,7 +7575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>429</v>
       </c>
@@ -7671,7 +7689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>430</v>
       </c>
@@ -7787,7 +7805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>435</v>
       </c>
@@ -7901,7 +7919,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>444</v>
       </c>
@@ -8015,7 +8033,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>454</v>
       </c>
@@ -8131,7 +8149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>461</v>
       </c>
@@ -8243,7 +8261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>464</v>
       </c>
@@ -8355,7 +8373,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>471</v>
       </c>
@@ -8469,7 +8487,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>482</v>
       </c>
@@ -8583,7 +8601,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>490</v>
       </c>
@@ -8697,7 +8715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>497</v>
       </c>
@@ -8811,7 +8829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>503</v>
       </c>
@@ -8925,7 +8943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>511</v>
       </c>
@@ -9037,7 +9055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>517</v>
       </c>
@@ -9149,7 +9167,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>524</v>
       </c>
@@ -9261,7 +9279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>528</v>
       </c>
@@ -9373,7 +9391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>529</v>
       </c>
@@ -9487,7 +9505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>530</v>
       </c>
@@ -9603,7 +9621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>531</v>
       </c>
@@ -9715,7 +9733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>538</v>
       </c>
@@ -9827,7 +9845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>543</v>
       </c>
@@ -9943,7 +9961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>552</v>
       </c>
@@ -10056,6 +10074,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN70">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI69">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
